--- a/file/table/DAPC_ProyectoBIM.xlsx
+++ b/file/table/DAPC_ProyectoBIM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CD3AD3-9F27-4A86-A7D0-9DB979FBB171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02403928-6CAE-4159-9C59-6A2C544F7FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57503" yWindow="6413" windowWidth="28994" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Metadata" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BIM!$E$5:$F$36</definedName>
     <definedName name="SumUDig">#REF!</definedName>
     <definedName name="UDig">BIM!$C$6</definedName>
   </definedNames>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>UDig</t>
   </si>
@@ -83,6 +84,30 @@
   </si>
   <si>
     <t>Código de alumno</t>
+  </si>
+  <si>
+    <t>B. Estructura</t>
+  </si>
+  <si>
+    <t>Columna ancho (m)</t>
+  </si>
+  <si>
+    <t>Columna largo (m)</t>
+  </si>
+  <si>
+    <t>Separación máxima (m)</t>
+  </si>
+  <si>
+    <t># de ejes horizontales (1, 2..)</t>
+  </si>
+  <si>
+    <t># de ejes verticales (A,B…)</t>
+  </si>
+  <si>
+    <t>Separación horizontal ejes (m)</t>
+  </si>
+  <si>
+    <t>Separación vertical ejes (m)</t>
   </si>
 </sst>
 </file>
@@ -247,7 +272,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -269,6 +294,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -559,13 +585,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA133A3-5F4C-48CF-BF69-9587FC94B6EF}">
-  <dimension ref="B1:E14"/>
+  <dimension ref="B1:E37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.06640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.1328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.59765625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.06640625" style="1"/>
+    <col min="4" max="4" width="9.06640625" style="1"/>
+    <col min="5" max="5" width="15" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.6">
@@ -576,23 +604,23 @@
       <c r="D1" s="2"/>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="13">
-        <v>2131321329</v>
+      <c r="C5" s="14">
+        <v>1000109401</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.6">
@@ -600,14 +628,19 @@
         <v>0</v>
       </c>
       <c r="C6" s="6">
-        <f>IFERROR(RIGHT(C5,1)*1,0)</f>
-        <v>9</v>
-      </c>
+        <f>IFERROR(_xlfn.FLOOR.MATH((RIGHT(C5,2)*1)^0.5),0)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="13"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="E8" s="13"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B9" s="7" t="s">
@@ -616,6 +649,7 @@
       <c r="C9" s="8" t="s">
         <v>12</v>
       </c>
+      <c r="E9" s="13"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B10" s="9" t="s">
@@ -623,8 +657,9 @@
       </c>
       <c r="C10" s="10">
         <f>7+UDig</f>
-        <v>16</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B11" s="9" t="s">
@@ -632,8 +667,9 @@
       </c>
       <c r="C11" s="10">
         <f>12+UDig</f>
-        <v>21</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="E11" s="13"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B12" s="9" t="s">
@@ -642,6 +678,7 @@
       <c r="C12" s="10">
         <v>1</v>
       </c>
+      <c r="E12" s="13"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B13" s="9" t="s">
@@ -650,10 +687,136 @@
       <c r="C13" s="10">
         <v>2</v>
       </c>
+      <c r="E13" s="13"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
+      <c r="E14" s="13"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="E15" s="13"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="13"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="13"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E18" s="13"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E19" s="13"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="E20" s="13"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="1">
+        <f>ROUNDUP((C11-C12-C13-C18/2-C18/2)/C20,0)</f>
+        <v>3</v>
+      </c>
+      <c r="E21" s="13"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="1">
+        <f>ROUNDUP((C10-C19/2-C19/2)/C20,0)</f>
+        <v>3</v>
+      </c>
+      <c r="E22" s="13"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="1">
+        <f>(C11-C12-C13-C18/2-C18/2)/C21</f>
+        <v>3.2333333333333329</v>
+      </c>
+      <c r="E23" s="13"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1">
+        <f>(C10-C19/2-C19/2)/C22</f>
+        <v>2.5666666666666664</v>
+      </c>
+      <c r="E24" s="13"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="E25" s="13"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="E26" s="13"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="E27" s="13"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="E28" s="13"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="E29" s="13"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="E30" s="13"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="E31" s="13"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="E32" s="13"/>
+    </row>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.6">
+      <c r="E33" s="13"/>
+    </row>
+    <row r="34" spans="5:5" x14ac:dyDescent="0.6">
+      <c r="E34" s="13"/>
+    </row>
+    <row r="35" spans="5:5" x14ac:dyDescent="0.6">
+      <c r="E35" s="13"/>
+    </row>
+    <row r="36" spans="5:5" x14ac:dyDescent="0.6">
+      <c r="E36" s="13"/>
+    </row>
+    <row r="37" spans="5:5" x14ac:dyDescent="0.6">
+      <c r="E37" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/file/table/DAPC_ProyectoBIM.xlsx
+++ b/file/table/DAPC_ProyectoBIM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02403928-6CAE-4159-9C59-6A2C544F7FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2558D3D2-B65F-49B4-98C3-1FEC55A8B348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57503" yWindow="6413" windowWidth="28994" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/file/table/DAPC_ProyectoBIM.xlsx
+++ b/file/table/DAPC_ProyectoBIM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2558D3D2-B65F-49B4-98C3-1FEC55A8B348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C388C4ED-CB7A-48B5-BF83-4BA097F34727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57503" yWindow="6413" windowWidth="28994" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,7 @@
     <definedName name="UDig">BIM!$C$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -56,9 +57,6 @@
     <t>Pass: 1234</t>
   </si>
   <si>
-    <t>v.20250810</t>
-  </si>
-  <si>
     <t>UECIJG / Dibujo asistido por computador - DAPC / Proyecto BIM</t>
   </si>
   <si>
@@ -108,6 +106,9 @@
   </si>
   <si>
     <t>Separación vertical ejes (m)</t>
+  </si>
+  <si>
+    <t>v.20251105</t>
   </si>
 </sst>
 </file>
@@ -294,8 +295,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -303,6 +303,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -585,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA133A3-5F4C-48CF-BF69-9587FC94B6EF}">
-  <dimension ref="B1:E37"/>
+  <dimension ref="B1:E27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
@@ -599,27 +602,27 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B1" s="2"/>
       <c r="C1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="14">
+        <v>12</v>
+      </c>
+      <c r="C5" s="13">
         <v>1000109401</v>
       </c>
     </row>
@@ -631,192 +634,142 @@
         <f>IFERROR(_xlfn.FLOOR.MATH((RIGHT(C5,2)*1)^0.5),0)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="13"/>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="13"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="13"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B10" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="10">
         <f>7+UDig</f>
         <v>8</v>
       </c>
-      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B11" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="10">
         <f>12+UDig</f>
         <v>13</v>
       </c>
-      <c r="E11" s="13"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B12" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="10">
         <v>1</v>
       </c>
-      <c r="E12" s="13"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B13" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="10">
         <v>2</v>
       </c>
-      <c r="E13" s="13"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
-      <c r="E14" s="13"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B16" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="13"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="13"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="10">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C19" s="10">
         <v>0.3</v>
       </c>
-      <c r="E18" s="13"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B20" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E19" s="13"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="10">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B21" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="E20" s="13"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="1">
+      <c r="C21" s="10">
         <f>ROUNDUP((C11-C12-C13-C18/2-C18/2)/C20,0)</f>
         <v>3</v>
       </c>
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="1">
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="10">
         <f>ROUNDUP((C10-C19/2-C19/2)/C20,0)</f>
         <v>3</v>
       </c>
-      <c r="E22" s="13"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="1">
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B23" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="10">
         <f>(C11-C12-C13-C18/2-C18/2)/C21</f>
         <v>3.2333333333333329</v>
       </c>
-      <c r="E23" s="13"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="1">
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B24" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="10">
         <f>(C10-C19/2-C19/2)/C22</f>
         <v>2.5666666666666664</v>
       </c>
-      <c r="E24" s="13"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="E25" s="13"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="E26" s="13"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="E27" s="13"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="E28" s="13"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="E29" s="13"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="E30" s="13"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="E31" s="13"/>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="E32" s="13"/>
-    </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.6">
-      <c r="E33" s="13"/>
-    </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.6">
-      <c r="E34" s="13"/>
-    </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.6">
-      <c r="E35" s="13"/>
-    </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.6">
-      <c r="E36" s="13"/>
-    </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.6">
-      <c r="E37" s="13"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B27" s="11"/>
+      <c r="C27" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/file/table/DAPC_ProyectoBIM.xlsx
+++ b/file/table/DAPC_ProyectoBIM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C388C4ED-CB7A-48B5-BF83-4BA097F34727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961828DA-03DB-4369-A5F9-C5D9C4BF5245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57503" yWindow="6413" windowWidth="28994" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/file/table/DAPC_ProyectoBIM.xlsx
+++ b/file/table/DAPC_ProyectoBIM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961828DA-03DB-4369-A5F9-C5D9C4BF5245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40271840-B5D2-4126-BFC3-098001B3A03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57503" yWindow="6413" windowWidth="28994" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>UDig</t>
   </si>
@@ -109,6 +109,12 @@
   </si>
   <si>
     <t>v.20251105</t>
+  </si>
+  <si>
+    <t>Viga ancho, b (m)</t>
+  </si>
+  <si>
+    <t>Viga alto, h (m)</t>
   </si>
 </sst>
 </file>
@@ -760,12 +766,20 @@
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B25" s="9"/>
-      <c r="C25" s="10"/>
+      <c r="B25" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="10">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B26" s="9"/>
-      <c r="C26" s="10"/>
+      <c r="B26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="10">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B27" s="11"/>

--- a/file/table/DAPC_ProyectoBIM.xlsx
+++ b/file/table/DAPC_ProyectoBIM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40271840-B5D2-4126-BFC3-098001B3A03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F71089-6BFF-4DFF-A7E6-C4B30DA96047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57503" yWindow="6413" windowWidth="28994" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/file/table/DAPC_ProyectoBIM.xlsx
+++ b/file/table/DAPC_ProyectoBIM.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29710"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F71089-6BFF-4DFF-A7E6-C4B30DA96047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E81D821-DDF1-4B93-A310-322AAE965CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57503" yWindow="6413" windowWidth="28994" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BIM" sheetId="8" r:id="rId1"/>
     <sheet name="Metadata" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BIM!$E$5:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BIM!$E$5:$F$35</definedName>
     <definedName name="SumUDig">#REF!</definedName>
-    <definedName name="UDig">BIM!$C$6</definedName>
+    <definedName name="UDig">BIM!$C$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,9 +44,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
-    <t>UDig</t>
-  </si>
-  <si>
     <t>Metadata</t>
   </si>
   <si>
@@ -81,9 +77,6 @@
     <t>Valor</t>
   </si>
   <si>
-    <t>Código de alumno</t>
-  </si>
-  <si>
     <t>B. Estructura</t>
   </si>
   <si>
@@ -108,20 +101,38 @@
     <t>Separación vertical ejes (m)</t>
   </si>
   <si>
-    <t>v.20251105</t>
-  </si>
-  <si>
     <t>Viga ancho, b (m)</t>
   </si>
   <si>
     <t>Viga alto, h (m)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ingrese su </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>SDig</t>
+    </r>
+  </si>
+  <si>
+    <t>Old witd student id: =IFERROR(FLOOR.MATH((RIGHT(C5,2)*1)^0.5),0)</t>
+  </si>
+  <si>
+    <t>v.20260113</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,6 +172,13 @@
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -279,7 +297,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -289,9 +307,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -307,11 +322,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -594,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA133A3-5F4C-48CF-BF69-9587FC94B6EF}">
-  <dimension ref="B1:E27"/>
+  <dimension ref="B1:E26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
@@ -608,17 +623,17 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B1" s="2"/>
       <c r="C1" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D1" s="2"/>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B2" s="15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="15"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B3" s="15"/>
@@ -626,164 +641,155 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="13">
-        <v>1000109401</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6">
-        <f>IFERROR(_xlfn.FLOOR.MATH((RIGHT(C5,2)*1)^0.5),0)</f>
+        <v>21</v>
+      </c>
+      <c r="C5" s="12">
         <v>1</v>
       </c>
     </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B8" s="1" t="s">
-        <v>7</v>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B10" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="10">
+      <c r="B9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="9">
         <f>7+UDig</f>
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B11" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="10">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="9">
         <f>12+UDig</f>
         <v>13</v>
       </c>
     </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9">
+        <v>1</v>
+      </c>
+    </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.6">
+      <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B13" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B17" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B18" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B17" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B18" s="9" t="s">
+      <c r="C18" s="9">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B19" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C19" s="9">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="9">
+        <f>ROUNDUP((C10-C11-C12-C17/2-C17/2)/C19,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B21" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="9">
+        <f>ROUNDUP((C9-C18/2-C18/2)/C19,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="9">
+        <f>(C10-C11-C12-C17/2-C17/2)/C20</f>
+        <v>3.2333333333333329</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="9">
+        <f>(C9-C18/2-C18/2)/C21</f>
+        <v>2.5666666666666664</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="9">
         <v>0.3</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="10">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B20" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="10">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="10">
-        <f>ROUNDUP((C11-C12-C13-C18/2-C18/2)/C20,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="10">
-        <f>ROUNDUP((C10-C19/2-C19/2)/C20,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B23" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="10">
-        <f>(C11-C12-C13-C18/2-C18/2)/C21</f>
-        <v>3.2333333333333329</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B24" s="9" t="s">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B25" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="10">
-        <f>(C10-C19/2-C19/2)/C22</f>
-        <v>2.5666666666666664</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B25" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="10">
-        <v>0.3</v>
+      <c r="C25" s="9">
+        <v>0.4</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B26" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="10">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B27" s="11"/>
-      <c r="C27" s="16"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -795,7 +801,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD4CBC5-BEDD-4E97-A57A-4EDFE72E7B14}">
-  <dimension ref="B1:B4"/>
+  <dimension ref="B1:B5"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="2.53125" style="1" customWidth="1"/>
@@ -808,17 +814,22 @@
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B4" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.6">
+      <c r="B5" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/file/table/DAPC_ProyectoBIM.xlsx
+++ b/file/table/DAPC_ProyectoBIM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29710"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E81D821-DDF1-4B93-A310-322AAE965CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D732EE-E7F9-4AE9-81F1-5D8215815E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
     <t>Old witd student id: =IFERROR(FLOOR.MATH((RIGHT(C5,2)*1)^0.5),0)</t>
   </si>
   <si>
-    <t>v.20260113</t>
+    <t>v.20260418</t>
   </si>
 </sst>
 </file>
@@ -665,8 +665,8 @@
         <v>4</v>
       </c>
       <c r="C9" s="9">
-        <f>7+UDig</f>
-        <v>8</v>
+        <f>9+UDig</f>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.6">
@@ -674,8 +674,8 @@
         <v>5</v>
       </c>
       <c r="C10" s="9">
-        <f>12+UDig</f>
-        <v>13</v>
+        <f>14+UDig</f>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.6">
@@ -683,7 +683,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="9">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.6">
@@ -691,7 +691,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="9">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.6">
@@ -741,7 +741,7 @@
       </c>
       <c r="C20" s="9">
         <f>ROUNDUP((C10-C11-C12-C17/2-C17/2)/C19,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.6">
@@ -759,7 +759,7 @@
       </c>
       <c r="C22" s="9">
         <f>(C10-C11-C12-C17/2-C17/2)/C20</f>
-        <v>3.2333333333333329</v>
+        <v>2.6749999999999998</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.6">
@@ -768,7 +768,7 @@
       </c>
       <c r="C23" s="9">
         <f>(C9-C18/2-C18/2)/C21</f>
-        <v>2.5666666666666664</v>
+        <v>3.2333333333333329</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.6">

--- a/file/table/DAPC_ProyectoBIM.xlsx
+++ b/file/table/DAPC_ProyectoBIM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D732EE-E7F9-4AE9-81F1-5D8215815E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC433A1-CF47-4D81-AEE5-9BF11C587B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/file/table/DAPC_ProyectoBIM.xlsx
+++ b/file/table/DAPC_ProyectoBIM.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC433A1-CF47-4D81-AEE5-9BF11C587B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25B79AD-6FDD-47CD-9C71-98C613E5AFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28898" yWindow="6368" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BIM" sheetId="8" r:id="rId1"/>
     <sheet name="Metadata" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BIM!$E$5:$F$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BIM!$E$5:$F$36</definedName>
     <definedName name="SumUDig">#REF!</definedName>
     <definedName name="UDig">BIM!$C$5</definedName>
   </definedNames>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Metadata</t>
   </si>
@@ -105,6 +105,15 @@
   </si>
   <si>
     <t>Viga alto, h (m)</t>
+  </si>
+  <si>
+    <t>Old witd student id: =IFERROR(FLOOR.MATH((RIGHT(C5,2)*1)^0.5),0)</t>
+  </si>
+  <si>
+    <t>v.20260418</t>
+  </si>
+  <si>
+    <t>Separación entrepisos (m)</t>
   </si>
   <si>
     <r>
@@ -120,12 +129,15 @@
       </rPr>
       <t>SDig</t>
     </r>
-  </si>
-  <si>
-    <t>Old witd student id: =IFERROR(FLOOR.MATH((RIGHT(C5,2)*1)^0.5),0)</t>
-  </si>
-  <si>
-    <t>v.20260418</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> &gt;&gt;&gt;&gt;&gt;</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -194,7 +206,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -292,12 +304,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -316,9 +354,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -328,6 +363,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -609,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA133A3-5F4C-48CF-BF69-9587FC94B6EF}">
-  <dimension ref="B1:E26"/>
+  <dimension ref="B1:E27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
@@ -623,27 +665,27 @@
     <row r="1" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B1" s="2"/>
       <c r="C1" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1" s="2"/>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="12">
+      <c r="B5" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="16">
         <v>1</v>
       </c>
     </row>
@@ -665,8 +707,8 @@
         <v>4</v>
       </c>
       <c r="C9" s="9">
-        <f>9+UDig</f>
-        <v>10</v>
+        <f>9.25+UDig</f>
+        <v>10.25</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.6">
@@ -674,15 +716,15 @@
         <v>5</v>
       </c>
       <c r="C10" s="9">
-        <f>14+UDig</f>
-        <v>15</v>
+        <f>13.75+UDig</f>
+        <v>14.75</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.6">
       <c r="B11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="15">
         <v>1.5</v>
       </c>
     </row>
@@ -690,7 +732,7 @@
       <c r="B12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="15">
         <v>2.5</v>
       </c>
     </row>
@@ -713,83 +755,91 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B17" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="9">
-        <v>0.3</v>
+        <v>23</v>
+      </c>
+      <c r="C17" s="15">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="9">
+        <v>12</v>
+      </c>
+      <c r="C18" s="15">
         <v>0.3</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="9">
-        <v>3.5</v>
+        <v>13</v>
+      </c>
+      <c r="C19" s="15">
+        <v>0.3</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B20" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="9">
-        <f>ROUNDUP((C10-C11-C12-C17/2-C17/2)/C19,0)</f>
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="C20" s="15">
+        <v>3.5</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B21" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" s="9">
-        <f>ROUNDUP((C9-C18/2-C18/2)/C19,0)</f>
+        <f>ROUNDUP((C10-C11-C12-C18/2-C18/2)/C20,0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B22" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="9">
-        <f>(C10-C11-C12-C17/2-C17/2)/C20</f>
-        <v>2.6749999999999998</v>
+        <f>ROUNDUP((C9-C19/2-C19/2)/C20,0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B23" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="9">
-        <f>(C9-C18/2-C18/2)/C21</f>
-        <v>3.2333333333333329</v>
+        <f>(C10-C11-C12-C18/2-C18/2)/C21</f>
+        <v>3.4833333333333329</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B24" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24" s="9">
-        <v>0.3</v>
+        <f>(C9-C19/2-C19/2)/C22</f>
+        <v>3.3166666666666664</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B25" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="15">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C26" s="15">
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B26" s="10"/>
-      <c r="C26" s="14"/>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B27" s="10"/>
+      <c r="C27" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -829,7 +879,7 @@
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/file/table/DAPC_ProyectoBIM.xlsx
+++ b/file/table/DAPC_ProyectoBIM.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25B79AD-6FDD-47CD-9C71-98C613E5AFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EABCCF-FCB7-4812-9C70-D2526379D084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="6368" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BIM" sheetId="8" r:id="rId1"/>
     <sheet name="Metadata" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BIM!$E$5:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BIM!#REF!</definedName>
     <definedName name="SumUDig">#REF!</definedName>
-    <definedName name="UDig">BIM!$C$5</definedName>
+    <definedName name="UDig">BIM!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -89,12 +89,6 @@
     <t>Separación máxima (m)</t>
   </si>
   <si>
-    <t># de ejes horizontales (1, 2..)</t>
-  </si>
-  <si>
-    <t># de ejes verticales (A,B…)</t>
-  </si>
-  <si>
     <t>Separación horizontal ejes (m)</t>
   </si>
   <si>
@@ -110,41 +104,26 @@
     <t>Old witd student id: =IFERROR(FLOOR.MATH((RIGHT(C5,2)*1)^0.5),0)</t>
   </si>
   <si>
-    <t>v.20260418</t>
-  </si>
-  <si>
     <t>Separación entrepisos (m)</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Ingrese su </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>SDig</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> &gt;&gt;&gt;&gt;&gt;</t>
-    </r>
+    <t>v.20260421</t>
+  </si>
+  <si>
+    <t>Código de alumno &gt;&gt;&gt;&gt;</t>
+  </si>
+  <si>
+    <t># de ejes verticales (A,B,C…)</t>
+  </si>
+  <si>
+    <t># de ejes horizontales (1,2,3...)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,13 +163,6 @@
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -335,7 +307,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -370,6 +342,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -651,119 +626,125 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA133A3-5F4C-48CF-BF69-9587FC94B6EF}">
-  <dimension ref="B1:E27"/>
+  <dimension ref="B1:D26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.1328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.06640625" style="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="1"/>
+    <col min="2" max="2" width="42.06640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.1328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="2.59765625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B1" s="2"/>
       <c r="C1" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="14"/>
+      <c r="C2" s="18"/>
       <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.6">
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B3" s="14"/>
       <c r="C3" s="14"/>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B5" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B7" s="1" t="s">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="16">
+        <v>1000142321</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B8" s="6" t="s">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="9">
+        <f>9.25+RIGHT(C4,1)</f>
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B9" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="9">
-        <f>9.25+UDig</f>
-        <v>10.25</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.6">
+        <f>12.75+MID(C4,9,1)</f>
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B10" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="9">
-        <f>13.75+UDig</f>
-        <v>14.75</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.6">
+        <v>8</v>
+      </c>
+      <c r="C10" s="15">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B11" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="15">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B12" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B13" s="10"/>
-      <c r="C13" s="11"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B15" s="1" t="s">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.6">
-      <c r="B16" s="6" t="s">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C15" s="7" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="15">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B17" s="8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B18" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="15">
         <v>0.3</v>
@@ -771,79 +752,71 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B19" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" s="15">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="15">
-        <v>3.5</v>
+        <v>24</v>
+      </c>
+      <c r="C20" s="9">
+        <f>ROUNDUP((C9-C10-C11-C17/2-C17/2)/C19,0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B21" s="8" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C21" s="9">
-        <f>ROUNDUP((C10-C11-C12-C18/2-C18/2)/C20,0)</f>
+        <f>ROUNDUP((C8-C18/2-C18/2)/C19,0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B22" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" s="9">
-        <f>ROUNDUP((C9-C19/2-C19/2)/C20,0)</f>
-        <v>3</v>
+        <f>(C9-C10-C11-C17/2-C17/2)/C20</f>
+        <v>3.4833333333333329</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B23" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="9">
-        <f>(C10-C11-C12-C18/2-C18/2)/C21</f>
-        <v>3.4833333333333329</v>
+        <f>(C8-C18/2-C18/2)/C21</f>
+        <v>3.3166666666666664</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B24" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="9">
-        <f>(C9-C19/2-C19/2)/C22</f>
-        <v>3.3166666666666664</v>
+        <v>17</v>
+      </c>
+      <c r="C24" s="15">
+        <v>0.3</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B25" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C25" s="15">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B26" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="15">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B27" s="10"/>
-      <c r="C27" s="13"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="B2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -879,7 +852,7 @@
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B5" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
